--- a/Playwright.xlsx
+++ b/Playwright.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3A5B13-FAD0-4C48-9B8D-AE3C364D508F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D589228-E148-4007-A312-8B870AD29257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="441">
   <si>
     <t>Actions</t>
   </si>
@@ -1539,12 +1539,601 @@
       <t xml:space="preserve"> used to remove the data from the server</t>
     </r>
   </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>What are Browser, BrowserContext, and Page in Playwright?</t>
+  </si>
+  <si>
+    <t>What is the difference between locator() and page.$() in Playwright?</t>
+  </si>
+  <si>
+    <t>What is auto wait in playwright?</t>
+  </si>
+  <si>
+    <t>What is the difference between fill() and type() in Playwright?</t>
+  </si>
+  <si>
+    <t>What is the difference between getByRole(), getByText(), and locator() in Playwright?</t>
+  </si>
+  <si>
+    <t>What is the difference between expect(locator).toBeVisible() and locator.isVisible()?</t>
+  </si>
+  <si>
+    <t>What's Playwright Test hooks?</t>
+  </si>
+  <si>
+    <t>What is the purpose of test.describe() in Playwright?</t>
+  </si>
+  <si>
+    <t>test.describe() is used to group related test cases together.</t>
+  </si>
+  <si>
+    <t>npx playwright codegen</t>
+  </si>
+  <si>
+    <t>npx playwright codegen opens a browser and records user actions such as clicks, typing, and navigation. Playwright automatically generates the corresponding automation script</t>
+  </si>
+  <si>
+    <t>What is the purpose of playwright.config.ts in a Playwright framework?</t>
+  </si>
+  <si>
+    <t>playwright.config.ts is the central configuration file in Playwright. It is used to manage framework-level settings such as browser configuration, base URL, timeouts, retries, reporters, projects (Chrome, Edge, Firefox), environment variable usage, screenshots, videos, traces, and parallel execution settings.</t>
+  </si>
+  <si>
+    <t>What is the difference between headless mode and headed mode in Playwright?</t>
+  </si>
+  <si>
+    <t>In headless mode, tests run without opening a visible browser window, making execution faster. In headed mode, the browser UI is displayed, which is useful for debugging and observing test execution.</t>
+  </si>
+  <si>
+    <t>What is storageState?</t>
+  </si>
+  <si>
+    <t>storageState is used to save and reuse browser authentication state, including cookies and local storage data. It helps avoid repeated logins and speeds up test execution.</t>
+  </si>
+  <si>
+    <t>What is the difference between:</t>
+  </si>
+  <si>
+    <t>locator('.item') creates a locator for all matching elements, while locator('.item').first() specifically targets the first matching element and is useful when multiple elements share the same locator.</t>
+  </si>
+  <si>
+    <t>innerText() returns only the visible text displayed to the user, whereas textContent() returns all text present in the DOM, including text from hidden elements.</t>
+  </si>
+  <si>
+    <t>isEnabled() is used to verify the enabled state and returns a boolean value, whereas toBeEnabled() is an assertion that automatically waits and fails the test if the element is not enabled.</t>
+  </si>
+  <si>
+    <t>Difference between : inner text(), text content(), all text content()</t>
+  </si>
+  <si>
+    <t>innerText() gets visible text from a single element. textContent() gets all text from a single element, including hidden text. allTextContents() gets text from all matching elements and returns it as an array.</t>
+  </si>
+  <si>
+    <t>What is the difference between first() and last()</t>
+  </si>
+  <si>
+    <t>first() selects the first matching element from a locator collection, whereas last() selects the last matching element from the same collection. They are useful when multiple elements match the locator and we need to interact with a specific one.</t>
+  </si>
+  <si>
+    <t>What is the difference between all the "wait for load state"?</t>
+  </si>
+  <si>
+    <t>waitForLoadState('load') waits until the page and its resources have finished loading.</t>
+  </si>
+  <si>
+    <t>waitForLoadState('networkidle') waits until the network activity becomes idle.</t>
+  </si>
+  <si>
+    <t>Domcontentloaded waits until the dom is loaded.</t>
+  </si>
+  <si>
+    <t>difference between :</t>
+  </si>
+  <si>
+    <t>await page.screenshot();</t>
+  </si>
+  <si>
+    <t>await locator.screenshot();</t>
+  </si>
+  <si>
+    <t>page.screenshot() - capture the whole screen</t>
+  </si>
+  <si>
+    <t>locator.screenshot() - captures the element screenshot</t>
+  </si>
+  <si>
+    <t>await page.close();</t>
+  </si>
+  <si>
+    <t>await browser.close();</t>
+  </si>
+  <si>
+    <t>page.close() : closes the page that's the tab of the browser</t>
+  </si>
+  <si>
+    <t>browse.close() : closes the whole browser session.</t>
+  </si>
+  <si>
+    <t>.fill() and .pressSequentially()</t>
+  </si>
+  <si>
+    <t>fill() clears the existing value and sets the new value directly, whereas pressSequentially() enters the text character by character, simulating actual keyboard typing.</t>
+  </si>
+  <si>
+    <t>difference between the below while handling checkbox</t>
+  </si>
+  <si>
+    <t>await locator.getAttribute('value');</t>
+  </si>
+  <si>
+    <t>await locator.inputValue();</t>
+  </si>
+  <si>
+    <t>getAttribute() retrieves the value of a specified HTML attribute, whereas inputValue() retrieves the current value present in an input field. inputValue() is more commonly used when validating user-entered data in text fields.</t>
+  </si>
+  <si>
+    <t>difference between the below while handling dropdown</t>
+  </si>
+  <si>
+    <t>await locator.selectOption('India');</t>
+  </si>
+  <si>
+    <t>await locator.click();</t>
+  </si>
+  <si>
+    <t>selectOption() is specifically used for HTML &lt;select&gt; dropdowns and directly selects an option by value, label, or index. click() is a generic click action. For custom dropdowns &lt;div&gt; &lt;ul&gt;, we typically click the dropdown and then click the desired option.</t>
+  </si>
+  <si>
+    <t>test.only()</t>
+  </si>
+  <si>
+    <t>test.skip()</t>
+  </si>
+  <si>
+    <t>test.only() executes only the specified test (or test group) and ignores all other tests. test.skip() marks a test as skipped, so it is not executed during the test run.</t>
+  </si>
+  <si>
+    <t>test.fail()</t>
+  </si>
+  <si>
+    <t>test.skip() prevents a test from executing. test.fail() marks a test as an expected failure, typically used for known defects or functionality under development.</t>
+  </si>
+  <si>
+    <t>test.fixme()</t>
+  </si>
+  <si>
+    <t>test.skip() is used to intentionally skip a test</t>
+  </si>
+  <si>
+    <t>test.fixme() is used for a test that is known to be broken or not yet implemented.</t>
+  </si>
+  <si>
+    <t>Both prevent execution, but fixme() communicates that the test requires fixing in the future.</t>
+  </si>
+  <si>
+    <t>handling newly opened page / window</t>
+  </si>
+  <si>
+    <t>There are two ways to handle a newly opened tab/window.</t>
+  </si>
+  <si>
+    <t>page.waitForEvent('popup') is used when a specific page action opens a new tab/window. context.waitForEvent('page') listens for any new page created within the browser context. Both return a Page object representing the new tab.</t>
+  </si>
+  <si>
+    <t>handling existing page / window</t>
+  </si>
+  <si>
+    <t>In Playwright, there is no switchToWindow() method like Selenium. Each browser tab is represented by a Page object. For existing tabs, we can get all open pages using page.context().pages() and interact with the required page object directly or bring it to the front using bringToFront().</t>
+  </si>
+  <si>
+    <t>What's POM</t>
+  </si>
+  <si>
+    <t>Page Object Model is a design pattern used to separate page locators and page actions from test scripts. It improves code reusability, maintainability, readability, and reduces duplication when application locators change.</t>
+  </si>
+  <si>
+    <t>What's Promise.all()</t>
+  </si>
+  <si>
+    <t>Promise.all() is used to run multiple asynchronous operations concurrently and wait until all of them are completed. In Playwright, it is commonly used to avoid race conditions when an action triggers an event such as navigation, popup opening, or a download.</t>
+  </si>
+  <si>
+    <t>await expect(locator).toBeAttached();</t>
+  </si>
+  <si>
+    <t>await expect(locator).toBeVisible();</t>
+  </si>
+  <si>
+    <t>toBeAttached() verifies that the element is present in the DOM, whereas toBeVisible() verifies that the element is both present in the DOM and visible to the user.</t>
+  </si>
+  <si>
+    <t>await expect(locator).toHaveValue('Admin');</t>
+  </si>
+  <si>
+    <t>await expect(locator).toHaveText('Admin');</t>
+  </si>
+  <si>
+    <t>toHaveValue() is used for input elements and validates the value present in the value attribute, whereas toHaveText() validates the visible text content of an element.</t>
+  </si>
+  <si>
+    <t>What is the difference between :</t>
+  </si>
+  <si>
+    <t>await locator.hover();</t>
+  </si>
+  <si>
+    <t>await locator.clik();</t>
+  </si>
+  <si>
+    <t>hover() moves the mouse pointer over an element and triggers hover-related actions such as tooltips or dropdown menus. click() performs a mouse click on the element and triggers its click action.</t>
+  </si>
+  <si>
+    <t>what does await locator.dragTo(target); do?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragTo() performs a drag-and-drop operation from a source element to a target element. </t>
+  </si>
+  <si>
+    <t>What does await locator.focus(); do?</t>
+  </si>
+  <si>
+    <t>focus() places keyboard focus on an element without performing a mouse click.</t>
+  </si>
+  <si>
+    <t>What does await locator.press('Enter'); do?</t>
+  </si>
+  <si>
+    <t>press('Enter') simulates pressing the Enter key on the keyboard. element. press() is useful for testing keyboard interactions and shortcuts</t>
+  </si>
+  <si>
+    <t>await locator.isChecked();</t>
+  </si>
+  <si>
+    <t>await expect(locator).toBeChecked();</t>
+  </si>
+  <si>
+    <t>ischecked return true/false and you need to handle the result in separate code.</t>
+  </si>
+  <si>
+    <t>toBeChecked() is an assertion that automatically waits and fails the test if the element is not checked.</t>
+  </si>
+  <si>
+    <t>await locator.isDisabled();</t>
+  </si>
+  <si>
+    <t>await expect(locator).toBeDisabled();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is disabled returns a boolean value where as to be disabled waits for the element and fails the test if it's not disabled. </t>
+  </si>
+  <si>
+    <t>What does locator.waitfor() do?</t>
+  </si>
+  <si>
+    <t>locator.waitFor() waits for a locator to satisfy a specific state (attached, visible, hidden, detached, etc.)</t>
+  </si>
+  <si>
+    <t>Difference between :</t>
+  </si>
+  <si>
+    <t>await expect(page).toHaveTitle();</t>
+  </si>
+  <si>
+    <t>page.title() fetches and returns the current page title as a string. expect(page).toHaveTitle() is an assertion that verifies the page title matches the expected value and automatically waits until it does, failing the test if it doesn't.</t>
+  </si>
+  <si>
+    <t>const currentUrl = page.url();</t>
+  </si>
+  <si>
+    <t>page.url() fetches and returns the current page URL as a string, whereas expect(page).toHaveURL() is an assertion that verifies the current URL matches the expected URL and automatically waits for it, failing the test if it doesn't match.</t>
+  </si>
+  <si>
+    <t>page.goBack();</t>
+  </si>
+  <si>
+    <t>page.goForward();</t>
+  </si>
+  <si>
+    <t>goBack() navigates to the previous page in browser history, whereas goForward() navigates to the next page in browser history.</t>
+  </si>
+  <si>
+    <t>What is the Difference between:</t>
+  </si>
+  <si>
+    <t>await locator.clear();</t>
+  </si>
+  <si>
+    <t>await locator.fill();</t>
+  </si>
+  <si>
+    <t>clear() is used only to remove the existing value from an input field, whereas fill() clears the field and enters a new value. Using fill('') can also be used to clear a field by providing an empty string.</t>
+  </si>
+  <si>
+    <t>What is the Difference between :</t>
+  </si>
+  <si>
+    <t>await locator.all();</t>
+  </si>
+  <si>
+    <t>await locator.count();</t>
+  </si>
+  <si>
+    <t>locator.all() returns an array of Locator objects for all matching elements, whereas locator.count() returns the total number of matching elements as a number.</t>
+  </si>
+  <si>
+    <t>What will this return</t>
+  </si>
+  <si>
+    <t>const items = await page.locator('.item').all();</t>
+  </si>
+  <si>
+    <t>console.log(items.length);</t>
+  </si>
+  <si>
+    <t>all() fetches all matching elements as an array of Locator objects.</t>
+  </si>
+  <si>
+    <t>items.length gives the number of elements in that array.</t>
+  </si>
+  <si>
+    <t>await locator.getAttribute('disabled');</t>
+  </si>
+  <si>
+    <t>getAttribute('disabled') retrieves the value of the disabled attribute from the element, whereas isDisabled() directly checks whether the element is disabled and returns a boolean value</t>
+  </si>
+  <si>
+    <t>How do you upload files ?</t>
+  </si>
+  <si>
+    <t>Using setInputFiles('file path');</t>
+  </si>
+  <si>
+    <t>-Directly uploads the specified file.</t>
+  </si>
+  <si>
+    <t>-No OS file explorer interaction is needed.</t>
+  </si>
+  <si>
+    <t>What is await locator.selectText()?</t>
+  </si>
+  <si>
+    <t>selectText() highlights all the existing text inside an input or editable element.</t>
+  </si>
+  <si>
+    <t>Similar to a user pressing Ctrl + A inside the field.</t>
+  </si>
+  <si>
+    <t>await locator.check();</t>
+  </si>
+  <si>
+    <t>await locator.setChecked(true);</t>
+  </si>
+  <si>
+    <t>check() is used to select a checkbox or radio button and ensures it is checked. setChecked() is more flexible because it can both check and uncheck an element by passing true or false.</t>
+  </si>
+  <si>
+    <t>How do you handle checkboxes?</t>
+  </si>
+  <si>
+    <t>There are two ways to handle checkboxes. Playwright provides check() and uncheck() methods to explicitly select or deselect checkboxes. Alternatively, setChecked(true) and setChecked(false) can be used to dynamically set the checkbox state.</t>
+  </si>
+  <si>
+    <t>await page.keyboard.press('Enter');</t>
+  </si>
+  <si>
+    <t>await locator.press('Enter');</t>
+  </si>
+  <si>
+    <t>page.keyboard.press('Enter') sends the Enter key to whichever element currently has focus on the page. locator.press('Enter') first focuses the specified locator and then sends the Enter key specifically to that element</t>
+  </si>
+  <si>
+    <t>What does scrollIntoViewIfNeeded() do?</t>
+  </si>
+  <si>
+    <t>scrollIntoViewIfNeeded() scrolls the page until the element becomes visible in the viewport (if it's not already visible)</t>
+  </si>
+  <si>
+    <t>await page.pause();</t>
+  </si>
+  <si>
+    <t>await page.waitForTimeout(5000);</t>
+  </si>
+  <si>
+    <t>page.pause() pauses test execution and opens the Playwright Inspector for debugging. Execution resumes only when manually continued. waitForTimeout(5000) simply waits for a fixed 5 seconds and then continues automatically.</t>
+  </si>
+  <si>
+    <t>What's const box = await locator.boundingBox();</t>
+  </si>
+  <si>
+    <t>boundingBox() is used to get an element's coordinates and dimensions. It is mainly used for advanced scenarios such as custom drag-and-drop operations, canvas-based applications, mouse position calculations, and visual validations."</t>
+  </si>
+  <si>
+    <t>"I haven't used it much in projects because Playwright provides higher-level methods like click(), dragTo(), and hover() that cover most scenarios."</t>
+  </si>
+  <si>
+    <t>await expect(locator).toHaveCount(5);</t>
+  </si>
+  <si>
+    <t>toHaveCount(5) is an assertion that validates there are exactly 5 matching elements and automatically waits until the count becomes 5</t>
+  </si>
+  <si>
+    <t>what is await locator.evaluate(...)</t>
+  </si>
+  <si>
+    <t>locator.evaluate() lets you execute JavaScript inside the browser page context on a specific element.</t>
+  </si>
+  <si>
+    <t>page.locator('.item').nth(0)</t>
+  </si>
+  <si>
+    <t>page.locator('.item').filter({ hasText: 'Admin' });</t>
+  </si>
+  <si>
+    <t>nth(0) selects the element based on its position/index among all matching elements, whereas filter({ hasText: 'Admin' }) narrows down the matching elements and keeps only those containing the specified text.</t>
+  </si>
+  <si>
+    <t>Diffference between :</t>
+  </si>
+  <si>
+    <t>await expect(locator).toContainText('Admin');</t>
+  </si>
+  <si>
+    <t>.toContainText : the element should have the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.toHavetext : the give text should exactly match the element text. </t>
+  </si>
+  <si>
+    <t>Difference between:</t>
+  </si>
+  <si>
+    <t>await locator.waitFor({ state: 'attached' });</t>
+  </si>
+  <si>
+    <t>await locator.waitFor({ state: 'visible' });</t>
+  </si>
+  <si>
+    <t>state attached wait untill the  element is attatched to the DOM,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state visible will wait untill the element is present in the dom and visible to the user. </t>
+  </si>
+  <si>
+    <t>In Playwright, what is the difference between:</t>
+  </si>
+  <si>
+    <t>locator()</t>
+  </si>
+  <si>
+    <t>elementHandle()</t>
+  </si>
+  <si>
+    <t>and why is locator() generally recommended for UI test automation?</t>
+  </si>
+  <si>
+    <t>locator() has built-in auto-waiting and retry mechanisms. It re-queries the element before actions like click(), fill(), or assertions, making tests more stable.</t>
+  </si>
+  <si>
+    <t>elementHandle() points to a specific DOM element at a specific moment. If the DOM changes, the handle can become stale, leading to flaky tests.</t>
+  </si>
+  <si>
+    <t>Therefore, Playwright recommends locator() for most UI automation because it improves reliability and reduces synchronization issues.</t>
+  </si>
+  <si>
+    <t>await locator.isVisible();</t>
+  </si>
+  <si>
+    <t>When would you use each?</t>
+  </si>
+  <si>
+    <t>expect(locator).toBeVisible() is an assertion. It automatically waits until the element becomes visible (up to the timeout) and fails the test if the condition is not met.</t>
+  </si>
+  <si>
+    <t>locator.isVisible() is a method that immediately returns a boolean (true or false). It does not act as a test assertion, so additional logic is required to handle the result.</t>
+  </si>
+  <si>
+    <t>Use toBeVisible() when verifying expected behavior in a test. Use isVisible() when making conditional decisions in the test flow.</t>
+  </si>
+  <si>
+    <t>What is Playwright?</t>
+  </si>
+  <si>
+    <t>Playwright is a modern end-to-end automation testing framework.
+Supports UI, API, database, mobile, parallel, and cross-browser testing within a single framework.
+Provides auto-waiting for elements, reducing flakiness and speeding up execution.
+Runs in both header and headerless mode.
+Works across Windows, macOS, Linux.
+Mobile testing support for Android (Chrome) and iOS (Safari).
+Includes rich debugging tools such as trace viewer, video recording, and screenshots.</t>
+  </si>
+  <si>
+    <t>What is parallel testing?</t>
+  </si>
+  <si>
+    <t>What are Fixtures?</t>
+  </si>
+  <si>
+    <t>What is cross browser testing?</t>
+  </si>
+  <si>
+    <t>Parallel testing means running multiple tests at the same time to reduce execution time. In Playwright, this is done using workers—each worker runs tests in its own isolated browser instance. Parallelism can be controlled at three levels: via CLI with --workers, globally in playwright.config.ts using workers and fullyParallel, and at the suite level with test.describe.configure. By default, spec files run in parallel, while tests inside a file run sequentially unless configured.</t>
+  </si>
+  <si>
+    <t>Cross‑browser testing means verifying that your application works consistently across different browsers (Chromium/Chrome, Firefox, Safari/WebKit, etc.). It ensures that features, layouts, and behaviors don’t break when users switch browsers.</t>
+  </si>
+  <si>
+    <t>Predefined, reusable objects that Playwright provides to your tests (like browser, context, page, request). They give you a ready‑to‑use environment without writing boilerplate setup/teardown code.</t>
+  </si>
+  <si>
+    <t>Teardown in Playwright means cleanup after tests. It’s handled with hooks like afterEach or afterAll to close browsers, clear cookies, or remove test data. We use teardown to keep tests isolated and avoid side effects, but we don’t put assertions or heavy logic there—it’s purely for cleanup.”</t>
+  </si>
+  <si>
+    <t>What is teardown?</t>
+  </si>
+  <si>
+    <t>Browser → The actual browser instance (Chromium, Firefox, WebKit).
+BrowserContext → An isolated browser session with its own cookies, local storage, and cache.
+Page → A single tab within a browser context.</t>
+  </si>
+  <si>
+    <t>locator() supports auto-waiting, retries, and re-evaluates the element before each action.
+page.$() returns an ElementHandle immediately and does not have the same auto-waiting capabilities.</t>
+  </si>
+  <si>
+    <t>Auto-waiting means Playwright automatically waits for elements to be ready before performing actions.
+Playwright will keep trying until: The element exists in the DOM, It is visible, It is enabled and It is stable.
+If these conditions are not met within the timeout (default: 30 seconds), you'll get a TimeoutError.</t>
+  </si>
+  <si>
+    <t>type() simulates real keyboard typing character by character - currently not used.
+fill() clears the field first and then sets the entire value at once.
+Now to enter char by char "pressSequentially" is used.</t>
+  </si>
+  <si>
+    <t>getByRole() → Locates elements using their accessibility role (button, textbox, checkbox, link, etc.).
+getByText() → Locates elements based on visible text.
+locator() → Generic locator that can use CSS selectors, Xpath and data attributes</t>
+  </si>
+  <si>
+    <t>expect(locator).toBeVisible() is an assertion. It automatically waits (up to the timeout) for the element to become visible and fails the test if it doesn't.
+locator.isVisible() is a method that returns a boolean (true/false). It does not fail the test by itself; you must handle the result in your code.</t>
+  </si>
+  <si>
+    <t>beforeAll, beforeEach, afterEach, and afterAll are Playwright Test hooks used to perform common setup before or after test execution. They help avoid code duplication and improve test maintainability.
+beforeAll → Once before all tests
+beforeEach → Before every test
+afterEach → After every test
+afterAll → Once after all tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the difference between:
+page.locator('.item')
+page.locator('.item').first()
+</t>
+  </si>
+  <si>
+    <t>What is the difference between:
+await locator.innerText();
+await locator.textContent();</t>
+  </si>
+  <si>
+    <t>What is the difference between: await locator.isEnabled(); and await expect(locator).toBeEnabled();</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1591,6 +2180,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1633,7 +2229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1672,6 +2268,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1683,9 +2306,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2076,7 +2696,7 @@
       <c r="B2" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="24" t="s">
         <v>143</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2091,7 +2711,7 @@
       <c r="B3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="3" t="s">
         <v>128</v>
       </c>
@@ -2104,7 +2724,7 @@
       <c r="B4" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="3"/>
       <c r="E4" s="6"/>
     </row>
@@ -2115,7 +2735,7 @@
       <c r="B5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="3" t="s">
         <v>129</v>
       </c>
@@ -2348,7 +2968,7 @@
       <c r="D22" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="25" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2365,7 +2985,7 @@
       <c r="D23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E23" s="17"/>
+      <c r="E23" s="26"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -2380,7 +3000,7 @@
       <c r="D24" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="17"/>
+      <c r="E24" s="26"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -2395,7 +3015,7 @@
       <c r="D25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E25" s="17"/>
+      <c r="E25" s="26"/>
     </row>
     <row r="26" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
@@ -2505,7 +3125,7 @@
       <c r="D33" s="3"/>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>85</v>
       </c>
@@ -2576,7 +3196,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>103</v>
       </c>
@@ -2706,51 +3326,51 @@
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="23" t="s">
         <v>197</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="25" t="s">
         <v>207</v>
       </c>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:5" ht="98" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="14"/>
+      <c r="A49" s="23"/>
       <c r="B49" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="23" t="s">
         <v>215</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="24" t="s">
         <v>222</v>
       </c>
       <c r="E50" s="6"/>
     </row>
     <row r="51" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="14"/>
+      <c r="A51" s="23"/>
       <c r="B51" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" ht="92.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2964,7 +3584,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="23" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -2975,7 +3595,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="11" t="s">
         <v>178</v>
       </c>
@@ -3093,9 +3713,9 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="109.81640625" style="18" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="20.1796875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="109.81640625" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3137,9 +3757,1347 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB10B79-AAE2-447A-8BC7-E9CFA9A7B8BA}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="19"/>
+    <col min="2" max="2" width="46.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="84.26953125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="80.08984375" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" s="18"/>
+    </row>
+    <row r="5" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="18"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="18"/>
+    </row>
+    <row r="16" spans="1:4" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="18"/>
+    </row>
+    <row r="17" spans="1:4" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D17" s="18"/>
+    </row>
+    <row r="18" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="22"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="22"/>
+    </row>
+    <row r="22" spans="1:4" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="20">
+        <v>20</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="20"/>
+      <c r="B24" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="20"/>
+      <c r="B25" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
+        <v>21</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D26" s="22"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="20"/>
+      <c r="B27" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D27" s="22"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="20"/>
+      <c r="B28" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="22"/>
+    </row>
+    <row r="29" spans="1:4" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="20">
+        <v>22</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D29" s="22"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="20"/>
+      <c r="B30" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="22"/>
+    </row>
+    <row r="31" spans="1:4" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="20">
+        <v>23</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D31" s="22"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="20"/>
+      <c r="B32" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="22"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="20"/>
+      <c r="B33" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+    </row>
+    <row r="34" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="20">
+        <v>24</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" s="22"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="20"/>
+      <c r="B35" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="22"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="20"/>
+      <c r="B36" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="22"/>
+    </row>
+    <row r="37" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="20">
+        <v>25</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D37" s="22"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="20"/>
+      <c r="B38" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="22"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="20"/>
+      <c r="B39" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="22"/>
+    </row>
+    <row r="40" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="20">
+        <v>26</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D40" s="22"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="20"/>
+      <c r="B41" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="20"/>
+      <c r="B42" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="22"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="20">
+        <v>27</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D43" s="22"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="20"/>
+      <c r="B44" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D44" s="22"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="20"/>
+      <c r="B45" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D45" s="22"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="20">
+        <v>28</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="22"/>
+    </row>
+    <row r="47" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D47" s="22"/>
+    </row>
+    <row r="48" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A48" s="17">
+        <v>29</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="17">
+        <v>30</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="17">
+        <v>31</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="20">
+        <v>32</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="20"/>
+      <c r="B52" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" s="21"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="20"/>
+      <c r="B53" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="21"/>
+    </row>
+    <row r="54" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="20">
+        <v>33</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="20"/>
+      <c r="B55" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C55" s="21"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="20"/>
+      <c r="B56" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C56" s="21"/>
+    </row>
+    <row r="57" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="20">
+        <v>34</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="20"/>
+      <c r="B58" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C58" s="21"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="20"/>
+      <c r="B59" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="C59" s="21"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="17">
+        <v>35</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="17">
+        <v>36</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="17">
+        <v>37</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="20">
+        <v>38</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="20"/>
+      <c r="B64" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="20"/>
+      <c r="B65" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="C65" s="16"/>
+    </row>
+    <row r="66" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="20">
+        <v>39</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="20"/>
+      <c r="B67" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C67" s="21"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="20"/>
+      <c r="B68" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C68" s="21"/>
+    </row>
+    <row r="69" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="17">
+        <v>40</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="59" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="20">
+        <v>41</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="20"/>
+      <c r="B71" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="21"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="20"/>
+      <c r="B72" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="C72" s="21"/>
+    </row>
+    <row r="73" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="20">
+        <v>42</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="20"/>
+      <c r="B74" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C74" s="21"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="20"/>
+      <c r="B75" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" s="21"/>
+    </row>
+    <row r="76" spans="1:3" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="20">
+        <v>43</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="20"/>
+      <c r="B77" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="C77" s="21"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="20"/>
+      <c r="B78" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C78" s="21"/>
+    </row>
+    <row r="79" spans="1:3" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="20">
+        <v>44</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="20"/>
+      <c r="B80" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="C80" s="21"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="20"/>
+      <c r="B81" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C81" s="21"/>
+    </row>
+    <row r="82" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="20">
+        <v>45</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="20"/>
+      <c r="B83" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="C83" s="21"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="20"/>
+      <c r="B84" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C84" s="21"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="20">
+        <v>46</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="20"/>
+      <c r="B86" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="20"/>
+      <c r="B87" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="C87" s="16"/>
+    </row>
+    <row r="88" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="20">
+        <v>47</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="20"/>
+      <c r="B89" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C89" s="21"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="20"/>
+      <c r="B90" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C90" s="21"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="20">
+        <v>48</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="20"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="20"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="20">
+        <v>49</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="20"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="16" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="20">
+        <v>50</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="20"/>
+      <c r="B97" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="C97" s="21"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="20"/>
+      <c r="B98" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="21"/>
+    </row>
+    <row r="99" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A99" s="17">
+        <v>51</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="20">
+        <v>52</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="20"/>
+      <c r="B101" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="C101" s="21"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="20"/>
+      <c r="B102" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="C102" s="21"/>
+    </row>
+    <row r="103" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A103" s="17">
+        <v>53</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="20">
+        <v>54</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="20"/>
+      <c r="B105" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="C105" s="21"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="20"/>
+      <c r="B106" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C106" s="21"/>
+    </row>
+    <row r="107" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A107" s="20">
+        <v>55</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A108" s="20"/>
+      <c r="B108" s="21"/>
+      <c r="C108" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="17">
+        <v>56</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A110" s="17">
+        <v>57</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="20">
+        <v>58</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="20"/>
+      <c r="B112" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="C112" s="21"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="20"/>
+      <c r="B113" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C113" s="21"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="20">
+        <v>59</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="20"/>
+      <c r="B115" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="20"/>
+      <c r="B116" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C116" s="16"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="20">
+        <v>60</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="20"/>
+      <c r="B118" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="20"/>
+      <c r="B119" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="C119" s="16"/>
+    </row>
+    <row r="120" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="20">
+        <v>61</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="20"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+    </row>
+    <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="20"/>
+      <c r="B122" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="20"/>
+      <c r="B123" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="C123" s="16"/>
+    </row>
+    <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="20"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="16" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="20"/>
+      <c r="B125" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="C125" s="16"/>
+    </row>
+    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="20">
+        <v>62</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="20"/>
+      <c r="B127" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C127" s="4"/>
+    </row>
+    <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="20"/>
+      <c r="B128" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="20"/>
+      <c r="B129" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="C129" s="16"/>
+    </row>
+    <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A130" s="20"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A131" s="15">
+        <v>63</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A132" s="15">
+        <v>64</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A133" s="15">
+        <v>65</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A134" s="15">
+        <v>66</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="67">
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="A120:A125"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="A111:A113"/>
+    <mergeCell ref="C111:C113"/>
+    <mergeCell ref="A114:A116"/>
+    <mergeCell ref="A117:A119"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="A100:A102"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A23:A25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>